--- a/fixtures/uploads/2026-09/std_master.xlsx
+++ b/fixtures/uploads/2026-09/std_master.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Singkong kulit</t>
+          <t>Singkong Kulit Premium</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -517,7 +517,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Singkong daging</t>
+          <t>Singkong Daging Premium</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -543,7 +543,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Minyak</t>
+          <t>Minyak Olein</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -595,7 +595,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Amonium</t>
+          <t>Ammonium Bicarbonate (TI)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>HDPE 0,03</t>
+          <t>HDPE IFL Putih Tipis 0,03</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>HDPE 0,05</t>
+          <t>HDPE IFL Putih Tebal 0,05</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -673,7 +673,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>HDPE 0,07</t>
+          <t>HDPE IFL Putih Tebal 0,07</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Packaging IFM</t>
+          <t>Karton Polos IFL</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -725,7 +725,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Other cost</t>
+          <t>Tali Rafia 1 kg</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -751,7 +751,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Other cost</t>
+          <t>Plakban 100 Yard</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -777,7 +777,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Other cost</t>
+          <t>Label FCC</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -803,7 +803,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Ubi</t>
+          <t>Ubi Ungu</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -829,7 +829,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Minyak</t>
+          <t>Minyak Olein</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>HDPE 0,07</t>
+          <t>HDPE IFL Putih Tebal 0,07</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Other cost</t>
+          <t>Plakban 100 Yard</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Other cost</t>
+          <t>Tali Rafia 1 kg</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -959,7 +959,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Other cost</t>
+          <t>Label WIP QKSP</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -985,7 +985,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Ubi</t>
+          <t>Ubi Orange Kulit Merah</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Minyak</t>
+          <t>Minyak Olein</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1063,7 +1063,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>HDPE 0,07</t>
+          <t>HDPE IFL Putih Tebal 0,07</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Other cost</t>
+          <t>Plakban 100 Yard</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Other cost</t>
+          <t>Tali Rafia 1 kg</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Other cost</t>
+          <t>Label WIP QKSO</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
